--- a/results/MC_Dist=Exp_n=300_LT=0.1_C=0.2_B=100.xlsx
+++ b/results/MC_Dist=Exp_n=300_LT=0.1_C=0.2_B=100.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -123,13 +123,16 @@
     <t xml:space="preserve">Gamma</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5,1</t>
+    <t xml:space="preserve">1,0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x1.mean</t>
   </si>
   <si>
     <t xml:space="preserve">x1.sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x2.mean</t>
@@ -545,22 +548,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.08060370795568</v>
+        <v>-1.08226023777397</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0806037079556787</v>
+        <v>-0.0822602377739654</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0326239829841739</v>
+        <v>0.0419072644415048</v>
       </c>
       <c r="E2" t="n">
-        <v>0.162452868838653</v>
+        <v>0.188402421553835</v>
       </c>
       <c r="F2" t="n">
-        <v>0.94</v>
+        <v>0.96</v>
       </c>
       <c r="G2" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -568,16 +571,16 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.02821220617183</v>
+        <v>-0.98390743933796</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.028212206171832</v>
+        <v>0.0160925606620401</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0206560335810313</v>
+        <v>0.0176512555621472</v>
       </c>
       <c r="E3" t="n">
-        <v>0.141635843363187</v>
+        <v>0.132544199045038</v>
       </c>
       <c r="F3" t="n">
         <v>0.96</v>
@@ -591,22 +594,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>1.58013702071334</v>
+        <v>1.06100087548857</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0801370207133425</v>
+        <v>0.0610008754885729</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0356098659554658</v>
+        <v>0.0347962761826163</v>
       </c>
       <c r="E4" t="n">
-        <v>0.171705420358414</v>
+        <v>0.177169579702509</v>
       </c>
       <c r="F4" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="G4" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="5">
@@ -614,19 +617,19 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1.30542513398004</v>
+        <v>1.09432068720416</v>
       </c>
       <c r="C5" t="n">
-        <v>0.30542513398004</v>
+        <v>0.294320687204156</v>
       </c>
       <c r="D5" t="n">
-        <v>0.215631315605263</v>
+        <v>0.195784386026586</v>
       </c>
       <c r="E5" t="n">
-        <v>0.351543211330934</v>
+        <v>0.332057739761649</v>
       </c>
       <c r="F5" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="G5" t="n">
         <v>0.97</v>
@@ -637,22 +640,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>2.01819559933581</v>
+        <v>2.01391466270614</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0181955993358103</v>
+        <v>0.0139146627061364</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00541195132661511</v>
+        <v>0.00538053488807022</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0716393287634845</v>
+        <v>0.0723830791784812</v>
       </c>
       <c r="F6" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -783,20 +786,20 @@
         <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -815,2325 +818,2325 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1.27987004758753</v>
+        <v>-0.909336060958086</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.15250993817532</v>
+        <v>-1.29335033331885</v>
       </c>
       <c r="C2" t="n">
-        <v>1.77566552405849</v>
+        <v>1.51121155642053</v>
       </c>
       <c r="D2" t="n">
-        <v>1.49289564925834</v>
+        <v>0.901194379806576</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.0071124752963</v>
+        <v>-1.45457851896238</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.78167355707131</v>
+        <v>-2.44465356002396</v>
       </c>
       <c r="G2" t="n">
-        <v>2.01755204964759</v>
+        <v>2.02122650686716</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-1.11161996908908</v>
+        <v>-0.828362817651053</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.974239972742862</v>
+        <v>-0.887188189918882</v>
       </c>
       <c r="C3" t="n">
-        <v>1.59228047965475</v>
+        <v>0.843838082229899</v>
       </c>
       <c r="D3" t="n">
-        <v>1.23654350547505</v>
+        <v>0.727978388143748</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.577920041035922</v>
+        <v>-1.18192357678896</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.20751810021625</v>
+        <v>-1.6674462971988</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04847483434735</v>
+        <v>1.98502632676809</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-1.26091264100747</v>
+        <v>-1.14885914478182</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.03091612777112</v>
+        <v>-1.1630247836456</v>
       </c>
       <c r="C4" t="n">
-        <v>1.61431505981743</v>
+        <v>1.2663090039422</v>
       </c>
       <c r="D4" t="n">
-        <v>1.35335946628908</v>
+        <v>1.28994083826018</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.716166691255986</v>
+        <v>-0.743455169740225</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.17297261303846</v>
+        <v>-1.33928549751437</v>
       </c>
       <c r="G4" t="n">
-        <v>2.00249381999944</v>
+        <v>2.03059748655822</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-1.02249500996194</v>
+        <v>-0.900300124778593</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.914620261432363</v>
+        <v>-0.842225562050721</v>
       </c>
       <c r="C5" t="n">
-        <v>1.56742528678694</v>
+        <v>0.690867788764561</v>
       </c>
       <c r="D5" t="n">
-        <v>1.24252719162836</v>
+        <v>0.900711300770942</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.17412241138174</v>
+        <v>-1.18005059072585</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.49645207212161</v>
+        <v>-1.68124557579227</v>
       </c>
       <c r="G5" t="n">
-        <v>2.03355119389196</v>
+        <v>2.00576474052122</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.17906429031376</v>
+        <v>-1.27067473406252</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.88356482369933</v>
+        <v>-1.15034379245089</v>
       </c>
       <c r="C6" t="n">
-        <v>1.53551297822907</v>
+        <v>1.10715309837028</v>
       </c>
       <c r="D6" t="n">
-        <v>1.68390931071756</v>
+        <v>1.61775039413458</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.592369211042485</v>
+        <v>-0.895889994385969</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.29184025359623</v>
+        <v>-1.31346568306747</v>
       </c>
       <c r="G6" t="n">
-        <v>2.07207613912885</v>
+        <v>1.91845675005604</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-1.23590618788475</v>
+        <v>-1.18422360515016</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.866785182610275</v>
+        <v>-1.03080367202076</v>
       </c>
       <c r="C7" t="n">
-        <v>1.55919713327633</v>
+        <v>1.09537522054774</v>
       </c>
       <c r="D7" t="n">
-        <v>1.74179094811146</v>
+        <v>1.16085242324097</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.765133315384711</v>
+        <v>-0.876718909667367</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.25996576220539</v>
+        <v>-2.05188697366207</v>
       </c>
       <c r="G7" t="n">
-        <v>2.07171469923052</v>
+        <v>2.0654624743467</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-1.03608547150214</v>
+        <v>-0.63432921015068</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.12074295048376</v>
+        <v>-1.01551160618246</v>
       </c>
       <c r="C8" t="n">
-        <v>1.79215481445203</v>
+        <v>0.91535236527209</v>
       </c>
       <c r="D8" t="n">
-        <v>0.84404842383467</v>
+        <v>0.231479578262407</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.686965936403914</v>
+        <v>-1.47435953232328</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.26415829603062</v>
+        <v>-2.6174967298978</v>
       </c>
       <c r="G8" t="n">
-        <v>2.04612571201425</v>
+        <v>1.85240650936974</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-1.09002580847404</v>
+        <v>-1.05906778539826</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.895875567563066</v>
+        <v>-1.08934876472301</v>
       </c>
       <c r="C9" t="n">
-        <v>1.30465785357422</v>
+        <v>1.02010562317287</v>
       </c>
       <c r="D9" t="n">
-        <v>1.66492707101453</v>
+        <v>1.18496882806016</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.806962742789403</v>
+        <v>-0.866982322557042</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.53468008478958</v>
+        <v>-1.4645876010208</v>
       </c>
       <c r="G9" t="n">
-        <v>2.09422002832853</v>
+        <v>2.04027430826009</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.942386222964409</v>
+        <v>-1.2966199648105</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.988324505890678</v>
+        <v>-0.877365361207342</v>
       </c>
       <c r="C10" t="n">
-        <v>1.55277638989022</v>
+        <v>1.0103767206013</v>
       </c>
       <c r="D10" t="n">
-        <v>1.17298997220951</v>
+        <v>1.171688176421</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.854501468882866</v>
+        <v>-0.628875267561488</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.66731703662873</v>
+        <v>-1.70423601657209</v>
       </c>
       <c r="G10" t="n">
-        <v>1.96664174459573</v>
+        <v>2.05762444717671</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.684164902139084</v>
+        <v>-0.898261875812775</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.15665664143959</v>
+        <v>-1.06158353020417</v>
       </c>
       <c r="C11" t="n">
-        <v>1.55473718096604</v>
+        <v>1.24606529741487</v>
       </c>
       <c r="D11" t="n">
-        <v>0.630003823449135</v>
+        <v>0.780729407900276</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.20407499189344</v>
+        <v>-1.21220390759175</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.70746922389426</v>
+        <v>-1.5426910931638</v>
       </c>
       <c r="G11" t="n">
-        <v>1.84898160615782</v>
+        <v>1.95989095882701</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.865288840804807</v>
+        <v>-0.817394738664634</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.08466631138273</v>
+        <v>-0.849984301222472</v>
       </c>
       <c r="C12" t="n">
-        <v>1.73466593980854</v>
+        <v>0.856313084400394</v>
       </c>
       <c r="D12" t="n">
-        <v>0.533254929074378</v>
+        <v>0.661238898528572</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.04384734332166</v>
+        <v>-1.23643159942913</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.28292234130732</v>
+        <v>-1.69208330892928</v>
       </c>
       <c r="G12" t="n">
-        <v>2.02416713318203</v>
+        <v>2.07999374921568</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-1.08844657339203</v>
+        <v>-0.932479603625139</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.9548504647954</v>
+        <v>-0.831921805582768</v>
       </c>
       <c r="C13" t="n">
-        <v>1.31763721409453</v>
+        <v>0.927484903460344</v>
       </c>
       <c r="D13" t="n">
-        <v>1.39257670215524</v>
+        <v>1.04151102994929</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.04593472100559</v>
+        <v>-1.02608803955344</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3023068059992</v>
+        <v>-1.74013365500675</v>
       </c>
       <c r="G13" t="n">
-        <v>2.04908762768768</v>
+        <v>2.01831896134059</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.928724657675265</v>
+        <v>-0.912842246199158</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.1592771417717</v>
+        <v>-0.839704867092312</v>
       </c>
       <c r="C14" t="n">
-        <v>1.66052974853237</v>
+        <v>0.84332829122138</v>
       </c>
       <c r="D14" t="n">
-        <v>1.12451582882562</v>
+        <v>0.835901700260652</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.28030325188802</v>
+        <v>-0.998203044427524</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.68361769427583</v>
+        <v>-1.59940799756826</v>
       </c>
       <c r="G14" t="n">
-        <v>2.02040971006568</v>
+        <v>2.0685303731756</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.824761871085118</v>
+        <v>-1.17096657406631</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.947184830368545</v>
+        <v>-0.944461548625579</v>
       </c>
       <c r="C15" t="n">
-        <v>1.67629514973107</v>
+        <v>1.02461638443872</v>
       </c>
       <c r="D15" t="n">
-        <v>0.763890710031693</v>
+        <v>1.06750464452432</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2616810401508</v>
+        <v>-0.442767526376085</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6315804811935</v>
+        <v>-1.06954960533828</v>
       </c>
       <c r="G15" t="n">
-        <v>2.17231998114767</v>
+        <v>2.09842770342708</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0.94571301000155</v>
+        <v>-1.26222136972144</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.85069881506678</v>
+        <v>-1.01545410417908</v>
       </c>
       <c r="C16" t="n">
-        <v>1.43583200597037</v>
+        <v>1.06636702423938</v>
       </c>
       <c r="D16" t="n">
-        <v>1.02830371853114</v>
+        <v>1.33878389879809</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.591403526980751</v>
+        <v>-0.345225368251139</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.51321014528576</v>
+        <v>-1.03447861566721</v>
       </c>
       <c r="G16" t="n">
-        <v>2.11445036769241</v>
+        <v>1.93279789482732</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.978343096035487</v>
+        <v>-1.43585005128386</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.0347686934954</v>
+        <v>-1.18860658570906</v>
       </c>
       <c r="C17" t="n">
-        <v>1.54964516530103</v>
+        <v>1.34457700876763</v>
       </c>
       <c r="D17" t="n">
-        <v>1.20189481203182</v>
+        <v>1.47077126264383</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.92424911794225</v>
+        <v>-0.204878899010125</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.44248309089804</v>
+        <v>-0.749090183707148</v>
       </c>
       <c r="G17" t="n">
-        <v>1.98444798613009</v>
+        <v>2.04897766600022</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-1.02134643190797</v>
+        <v>-1.04951236167776</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.09476941216038</v>
+        <v>-0.855765764289877</v>
       </c>
       <c r="C18" t="n">
-        <v>1.63037475354947</v>
+        <v>0.976091583477817</v>
       </c>
       <c r="D18" t="n">
-        <v>1.25034805628335</v>
+        <v>1.15807249357746</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2225597731273</v>
+        <v>-0.880284579645333</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.33520469700679</v>
+        <v>-1.30799136146044</v>
       </c>
       <c r="G18" t="n">
-        <v>2.05442638235202</v>
+        <v>2.04758893571247</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-1.20587816228398</v>
+        <v>-0.838603860200675</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.06897327408559</v>
+        <v>-0.921008323290775</v>
       </c>
       <c r="C19" t="n">
-        <v>1.62970287857354</v>
+        <v>0.915577646105032</v>
       </c>
       <c r="D19" t="n">
-        <v>1.43570419234925</v>
+        <v>0.70650900287468</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.944792644823729</v>
+        <v>-1.08294990102624</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.70318250165213</v>
+        <v>-1.55938392364714</v>
       </c>
       <c r="G19" t="n">
-        <v>2.11718845525803</v>
+        <v>2.04108894113021</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-1.04279633353899</v>
+        <v>-1.05644194241005</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.943594342974241</v>
+        <v>-0.77244104524504</v>
       </c>
       <c r="C20" t="n">
-        <v>1.39738840189701</v>
+        <v>0.878128583305848</v>
       </c>
       <c r="D20" t="n">
-        <v>1.07423382443333</v>
+        <v>1.11697878194151</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.82120383182464</v>
+        <v>-1.01842775868805</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.31242779740234</v>
+        <v>-1.50188405060054</v>
       </c>
       <c r="G20" t="n">
-        <v>1.99352590756266</v>
+        <v>2.070602437303</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-1.21123589371037</v>
+        <v>-1.21228295358966</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.14747863459424</v>
+        <v>-0.822832974922499</v>
       </c>
       <c r="C21" t="n">
-        <v>1.73062026797308</v>
+        <v>0.86067838310592</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5867571978911</v>
+        <v>1.1246801585423</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.736614387225874</v>
+        <v>-0.974286782858206</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.25314732395303</v>
+        <v>-1.84290981964096</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9466922299825</v>
+        <v>2.05908507206129</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-1.09183767780941</v>
+        <v>-1.07221264526833</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.2323423954717</v>
+        <v>-0.807446971097186</v>
       </c>
       <c r="C22" t="n">
-        <v>1.68643141433927</v>
+        <v>0.895008177114492</v>
       </c>
       <c r="D22" t="n">
-        <v>0.95449098830677</v>
+        <v>1.28609533670321</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.88018724493946</v>
+        <v>-1.00568654221753</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.08845040776281</v>
+        <v>-2.39948146040013</v>
       </c>
       <c r="G22" t="n">
-        <v>1.97442529676346</v>
+        <v>2.10048490220228</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.777138600295799</v>
+        <v>-1.1821285483888</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.02979251444965</v>
+        <v>-0.9443809843414</v>
       </c>
       <c r="C23" t="n">
-        <v>1.49562835507839</v>
+        <v>1.05709047481251</v>
       </c>
       <c r="D23" t="n">
-        <v>0.862817307203309</v>
+        <v>1.20405016403785</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.01514389168972</v>
+        <v>-0.602355328153752</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.70493416082702</v>
+        <v>-1.2172235835217</v>
       </c>
       <c r="G23" t="n">
-        <v>2.0016981232323</v>
+        <v>2.05777550303764</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-0.919945528170239</v>
+        <v>-1.0783643626324</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.884283181173461</v>
+        <v>-1.36317704479212</v>
       </c>
       <c r="C24" t="n">
-        <v>1.40256090252542</v>
+        <v>1.44107310002137</v>
       </c>
       <c r="D24" t="n">
-        <v>0.861701004213577</v>
+        <v>0.932184464183892</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.999016480000255</v>
+        <v>-1.05477758155674</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.45480647818945</v>
+        <v>-2.03437680793098</v>
       </c>
       <c r="G24" t="n">
-        <v>2.10306077389717</v>
+        <v>1.98289781416378</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-1.10318889321133</v>
+        <v>-0.681703636647432</v>
       </c>
       <c r="B25" t="n">
-        <v>-1.13764533173303</v>
+        <v>-0.892611868010616</v>
       </c>
       <c r="C25" t="n">
-        <v>1.74090531072834</v>
+        <v>1.11260466186791</v>
       </c>
       <c r="D25" t="n">
-        <v>1.39025473807563</v>
+        <v>0.582491535366043</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.08222526061282</v>
+        <v>-1.53647401772658</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.24238893887435</v>
+        <v>-1.98338838448836</v>
       </c>
       <c r="G25" t="n">
-        <v>1.93043749727961</v>
+        <v>2.07336508993238</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-1.38114686891152</v>
+        <v>-1.32516977139116</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.850763310346743</v>
+        <v>-0.90696360404749</v>
       </c>
       <c r="C26" t="n">
-        <v>1.46370833164315</v>
+        <v>1.0261906023959</v>
       </c>
       <c r="D26" t="n">
-        <v>1.98148703402792</v>
+        <v>1.47234040111911</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.545335547245309</v>
+        <v>-0.586676988914717</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.17225291732573</v>
+        <v>-1.13412995364675</v>
       </c>
       <c r="G26" t="n">
-        <v>1.97219125821753</v>
+        <v>2.09802495403168</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.96066044614249</v>
+        <v>-1.07471533945321</v>
       </c>
       <c r="B27" t="n">
-        <v>-1.42652929559968</v>
+        <v>-1.05124819474907</v>
       </c>
       <c r="C27" t="n">
-        <v>1.93781486190496</v>
+        <v>1.0432455568919</v>
       </c>
       <c r="D27" t="n">
-        <v>1.01538690005851</v>
+        <v>1.23534790941946</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.23155662630678</v>
+        <v>-1.13518603237519</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.1500691332966</v>
+        <v>-2.19615150565729</v>
       </c>
       <c r="G27" t="n">
-        <v>1.93490743665826</v>
+        <v>2.01735023048893</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-1.0842139723489</v>
+        <v>-1.33074631629796</v>
       </c>
       <c r="B28" t="n">
-        <v>-1.23858715926748</v>
+        <v>-0.953754160634759</v>
       </c>
       <c r="C28" t="n">
-        <v>1.8664184945574</v>
+        <v>1.04176131963717</v>
       </c>
       <c r="D28" t="n">
-        <v>1.22544438824788</v>
+        <v>1.55041401014945</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.423051498961823</v>
+        <v>-0.479965809371332</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.31544992327907</v>
+        <v>-1.06052128647451</v>
       </c>
       <c r="G28" t="n">
-        <v>2.00835575239103</v>
+        <v>1.95708979252822</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-0.901234842460051</v>
+        <v>-1.07342205190146</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.962260152011628</v>
+        <v>-0.953148043885414</v>
       </c>
       <c r="C29" t="n">
-        <v>1.46915098896598</v>
+        <v>1.12079499678752</v>
       </c>
       <c r="D29" t="n">
-        <v>1.20676989108733</v>
+        <v>0.97237340271584</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.977404976818657</v>
+        <v>-0.981120333486044</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.63909701266016</v>
+        <v>-1.31321734046807</v>
       </c>
       <c r="G29" t="n">
-        <v>1.99719558100066</v>
+        <v>1.92901531822135</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-1.17472768998988</v>
+        <v>-1.17951908622262</v>
       </c>
       <c r="B30" t="n">
-        <v>-1.14229544445549</v>
+        <v>-0.914913295420373</v>
       </c>
       <c r="C30" t="n">
-        <v>1.89569175017532</v>
+        <v>0.8982108267647</v>
       </c>
       <c r="D30" t="n">
-        <v>1.44242425535997</v>
+        <v>1.4599043267228</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.816916489591893</v>
+        <v>-1.09381821971233</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.33408385669266</v>
+        <v>-2.10269592977478</v>
       </c>
       <c r="G30" t="n">
-        <v>1.95863038923818</v>
+        <v>1.95927167441675</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-1.38964731648501</v>
+        <v>-0.79997721038757</v>
       </c>
       <c r="B31" t="n">
-        <v>-1.01564876875059</v>
+        <v>-0.832072536855199</v>
       </c>
       <c r="C31" t="n">
-        <v>1.52408801839183</v>
+        <v>1.13449542763392</v>
       </c>
       <c r="D31" t="n">
-        <v>1.84442542937082</v>
+        <v>0.446889806904922</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.533991302207684</v>
+        <v>-1.05393748677021</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.01565617930495</v>
+        <v>-1.58743779116212</v>
       </c>
       <c r="G31" t="n">
-        <v>2.02629569899684</v>
+        <v>2.19694389812347</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-1.39129343241529</v>
+        <v>-1.29477307504383</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.944772280995992</v>
+        <v>-1.16884272674207</v>
       </c>
       <c r="C32" t="n">
-        <v>1.40986676398883</v>
+        <v>1.17364157838445</v>
       </c>
       <c r="D32" t="n">
-        <v>1.96992871586896</v>
+        <v>1.26777679772568</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.550800982614226</v>
+        <v>-0.726503831127493</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.15120444153715</v>
+        <v>-1.78178588510026</v>
       </c>
       <c r="G32" t="n">
-        <v>2.06434253794581</v>
+        <v>1.9158197645</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-1.26005625679207</v>
+        <v>-1.22295376120783</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.34211101333605</v>
+        <v>-1.07829060581933</v>
       </c>
       <c r="C33" t="n">
-        <v>1.73451337501582</v>
+        <v>1.28543780013221</v>
       </c>
       <c r="D33" t="n">
-        <v>1.72606644960185</v>
+        <v>1.38392938215073</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.958891837982464</v>
+        <v>-0.574385606019773</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.03330146290502</v>
+        <v>-1.14001480181396</v>
       </c>
       <c r="G33" t="n">
-        <v>1.97100781958095</v>
+        <v>2.00335020068346</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-1.15270383314798</v>
+        <v>-1.06679149818431</v>
       </c>
       <c r="B34" t="n">
-        <v>-1.13104282574074</v>
+        <v>-0.878844348540224</v>
       </c>
       <c r="C34" t="n">
-        <v>1.71451480073664</v>
+        <v>0.928612949146087</v>
       </c>
       <c r="D34" t="n">
-        <v>1.10327183342016</v>
+        <v>1.12832756934646</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.736164852016802</v>
+        <v>-1.11009420744333</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.11189334620313</v>
+        <v>-1.4768530528557</v>
       </c>
       <c r="G34" t="n">
-        <v>1.99214993333612</v>
+        <v>2.02746372027073</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.959570176285396</v>
+        <v>-1.08991130780772</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.20611157505343</v>
+        <v>-0.9865615293172</v>
       </c>
       <c r="C35" t="n">
-        <v>1.61456795613404</v>
+        <v>1.18550492869243</v>
       </c>
       <c r="D35" t="n">
-        <v>0.860656919248204</v>
+        <v>1.01731716598413</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.10786568331625</v>
+        <v>-0.999717986244845</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.20210708282644</v>
+        <v>-1.40267250212098</v>
       </c>
       <c r="G35" t="n">
-        <v>1.84471812712097</v>
+        <v>2.01586237562281</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-0.878446983730756</v>
+        <v>-1.29665809204285</v>
       </c>
       <c r="B36" t="n">
-        <v>-1.21216647216788</v>
+        <v>-1.12068006107602</v>
       </c>
       <c r="C36" t="n">
-        <v>1.84619450692895</v>
+        <v>1.34390567474192</v>
       </c>
       <c r="D36" t="n">
-        <v>0.770137660817423</v>
+        <v>1.46094532274277</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.16569425845845</v>
+        <v>-0.728372341101481</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.54676070880882</v>
+        <v>-1.19852099015681</v>
       </c>
       <c r="G36" t="n">
-        <v>1.97540783061122</v>
+        <v>1.9482998519383</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-1.33085253529822</v>
+        <v>-1.25307396651297</v>
       </c>
       <c r="B37" t="n">
-        <v>-1.00384137407994</v>
+        <v>-1.07758392965154</v>
       </c>
       <c r="C37" t="n">
-        <v>1.51654540004558</v>
+        <v>1.24945446656054</v>
       </c>
       <c r="D37" t="n">
-        <v>1.83706767555695</v>
+        <v>1.29582207683063</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.780981153122311</v>
+        <v>-0.790357216759432</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.20292631795427</v>
+        <v>-1.26209820791378</v>
       </c>
       <c r="G37" t="n">
-        <v>1.96072500906264</v>
+        <v>2.03180148932385</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-0.978213860619698</v>
+        <v>-0.954942787418196</v>
       </c>
       <c r="B38" t="n">
-        <v>-1.03207281948025</v>
+        <v>-0.817175527199462</v>
       </c>
       <c r="C38" t="n">
-        <v>1.70036152702914</v>
+        <v>0.788792652504632</v>
       </c>
       <c r="D38" t="n">
-        <v>0.972626117983601</v>
+        <v>0.930038958434854</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.885570287458183</v>
+        <v>-1.22521342349537</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.45824671731378</v>
+        <v>-1.71069993609191</v>
       </c>
       <c r="G38" t="n">
-        <v>1.99618682271923</v>
+        <v>1.94660606217677</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-0.99100422590069</v>
+        <v>-0.9386624887944</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.767103746475611</v>
+        <v>-0.917858186327031</v>
       </c>
       <c r="C39" t="n">
-        <v>1.2223197112474</v>
+        <v>0.997770963842327</v>
       </c>
       <c r="D39" t="n">
-        <v>1.24970436306198</v>
+        <v>0.773790205686838</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.884952821676468</v>
+        <v>-1.02621722248311</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.50333319987116</v>
+        <v>-1.48472707760843</v>
       </c>
       <c r="G39" t="n">
-        <v>2.18095261207396</v>
+        <v>2.01035138133984</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-1.13954070497492</v>
+        <v>-0.962250128171492</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.10043985298113</v>
+        <v>-0.887471097064579</v>
       </c>
       <c r="C40" t="n">
-        <v>1.60642857696362</v>
+        <v>1.00984755993691</v>
       </c>
       <c r="D40" t="n">
-        <v>1.1799697050634</v>
+        <v>1.09409235493389</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.930058226268791</v>
+        <v>-1.11869601845367</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.94847941742795</v>
+        <v>-1.58615384031097</v>
       </c>
       <c r="G40" t="n">
-        <v>2.03352733297249</v>
+        <v>1.95094971851099</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-1.2011171077225</v>
+        <v>-1.39071940527213</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.97604153758632</v>
+        <v>-0.942921772675824</v>
       </c>
       <c r="C41" t="n">
-        <v>1.61599709026701</v>
+        <v>0.94281161268621</v>
       </c>
       <c r="D41" t="n">
-        <v>1.59447653051077</v>
+        <v>1.37143568064693</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.854136445956724</v>
+        <v>-0.466498085259787</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.43106164672953</v>
+        <v>-1.08280249912971</v>
       </c>
       <c r="G41" t="n">
-        <v>2.0477987262804</v>
+        <v>2.00772235123125</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-0.947414268189781</v>
+        <v>-1.2956235806493</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.861688356827497</v>
+        <v>-0.937643216500043</v>
       </c>
       <c r="C42" t="n">
-        <v>1.27105818321585</v>
+        <v>0.93857814804101</v>
       </c>
       <c r="D42" t="n">
-        <v>1.06471196457876</v>
+        <v>1.72550743616613</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.11911507080386</v>
+        <v>-0.749210658797969</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.52148278865757</v>
+        <v>-1.27137441770776</v>
       </c>
       <c r="G42" t="n">
-        <v>2.10160163347507</v>
+        <v>2.03052073116563</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-1.01230450850001</v>
+        <v>-1.1082079933798</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.880585938303541</v>
+        <v>-1.08761802029195</v>
       </c>
       <c r="C43" t="n">
-        <v>1.44047359548023</v>
+        <v>1.01272968265183</v>
       </c>
       <c r="D43" t="n">
-        <v>1.44583605505871</v>
+        <v>1.30292969816926</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.11002154911625</v>
+        <v>-1.17809376066344</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.60795131049924</v>
+        <v>-1.38733306547065</v>
       </c>
       <c r="G43" t="n">
-        <v>1.99937166745164</v>
+        <v>2.03647344679278</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-1.15080522727224</v>
+        <v>-0.951774365479734</v>
       </c>
       <c r="B44" t="n">
-        <v>-1.26230675866921</v>
+        <v>-0.970245137762474</v>
       </c>
       <c r="C44" t="n">
-        <v>1.824624075478</v>
+        <v>1.05797706866213</v>
       </c>
       <c r="D44" t="n">
-        <v>1.40188861369825</v>
+        <v>0.862830102906262</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.13868039660295</v>
+        <v>-0.976496300004266</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.12974969864354</v>
+        <v>-1.49071686666091</v>
       </c>
       <c r="G44" t="n">
-        <v>2.00812939415987</v>
+        <v>2.04894528250935</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-1.08157168328716</v>
+        <v>-1.31131717250728</v>
       </c>
       <c r="B45" t="n">
-        <v>-1.0928777214081</v>
+        <v>-0.814252930696209</v>
       </c>
       <c r="C45" t="n">
-        <v>1.60971664424268</v>
+        <v>0.774471306879044</v>
       </c>
       <c r="D45" t="n">
-        <v>1.29829796652283</v>
+        <v>1.36274570492325</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.585609704871332</v>
+        <v>-0.655937653432595</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.27463286099061</v>
+        <v>-0.979745387689206</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03026491126239</v>
+        <v>2.02492503172847</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-1.27043115403861</v>
+        <v>-1.15109769436771</v>
       </c>
       <c r="B46" t="n">
-        <v>-1.13704247099361</v>
+        <v>-0.937604307338952</v>
       </c>
       <c r="C46" t="n">
-        <v>1.81321362721389</v>
+        <v>1.09287637346599</v>
       </c>
       <c r="D46" t="n">
-        <v>1.85700222639171</v>
+        <v>1.1745456604343</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.623360969229181</v>
+        <v>-1.01514713280018</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.19837124361745</v>
+        <v>-1.2603233594986</v>
       </c>
       <c r="G46" t="n">
-        <v>2.09480250048068</v>
+        <v>2.01280364126012</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-1.22794261145142</v>
+        <v>-0.95734059330375</v>
       </c>
       <c r="B47" t="n">
-        <v>-1.14400330740231</v>
+        <v>-1.14301018864241</v>
       </c>
       <c r="C47" t="n">
-        <v>1.59981523051379</v>
+        <v>1.1537419249194</v>
       </c>
       <c r="D47" t="n">
-        <v>1.42219147390152</v>
+        <v>0.994204880048008</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.622142913970882</v>
+        <v>-1.17346076444104</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.11938908924738</v>
+        <v>-1.62958545684486</v>
       </c>
       <c r="G47" t="n">
-        <v>2.04724735887753</v>
+        <v>1.94974003737237</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-1.00863358103969</v>
+        <v>-1.19756883136648</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.890739166082997</v>
+        <v>-0.881292287003312</v>
       </c>
       <c r="C48" t="n">
-        <v>1.37964473722025</v>
+        <v>1.01001538469187</v>
       </c>
       <c r="D48" t="n">
-        <v>1.29077844318478</v>
+        <v>1.40311340907686</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.09816240502838</v>
+        <v>-0.774462132353043</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.47026737838577</v>
+        <v>-1.31261149521977</v>
       </c>
       <c r="G48" t="n">
-        <v>2.15606295252702</v>
+        <v>1.99366525876304</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-1.30074071191266</v>
+        <v>-1.28769347797501</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.94032896143745</v>
+        <v>-1.0072651880683</v>
       </c>
       <c r="C49" t="n">
-        <v>1.4239485486845</v>
+        <v>1.05197394866607</v>
       </c>
       <c r="D49" t="n">
-        <v>1.8026018390371</v>
+        <v>1.4887769722867</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.600164646818421</v>
+        <v>-0.435441055541735</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.07126862278029</v>
+        <v>-1.13471365394781</v>
       </c>
       <c r="G49" t="n">
-        <v>2.08519978228255</v>
+        <v>1.93889588445821</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-1.10662547903523</v>
+        <v>-0.818839620186038</v>
       </c>
       <c r="B50" t="n">
-        <v>-1.20257509919131</v>
+        <v>-1.19164286576748</v>
       </c>
       <c r="C50" t="n">
-        <v>1.83654387649461</v>
+        <v>1.31445321619224</v>
       </c>
       <c r="D50" t="n">
-        <v>1.43897440710959</v>
+        <v>0.636122235342947</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.12263748272151</v>
+        <v>-1.1166638454137</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.03856605686267</v>
+        <v>-1.67021764865061</v>
       </c>
       <c r="G50" t="n">
-        <v>1.98559304018104</v>
+        <v>1.94638099050492</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-0.789326317778848</v>
+        <v>-1.26693514858595</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.840254550604538</v>
+        <v>-0.983148109743582</v>
       </c>
       <c r="C51" t="n">
-        <v>1.40270711864827</v>
+        <v>1.14759456978641</v>
       </c>
       <c r="D51" t="n">
-        <v>0.784088058798919</v>
+        <v>1.45889551797578</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.04032316454665</v>
+        <v>-0.527783186771513</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.68745680871674</v>
+        <v>-1.07068969850582</v>
       </c>
       <c r="G51" t="n">
-        <v>2.01962659001174</v>
+        <v>2.15450270500484</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-1.07145315547717</v>
+        <v>-1.06127842972146</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.818818377701559</v>
+        <v>-1.0120425347766</v>
       </c>
       <c r="C52" t="n">
-        <v>1.39532963358214</v>
+        <v>1.14124302217946</v>
       </c>
       <c r="D52" t="n">
-        <v>1.51767653399646</v>
+        <v>1.28885068521879</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.1927244614689</v>
+        <v>-0.741519318403716</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.18423466647958</v>
+        <v>-1.52211586066336</v>
       </c>
       <c r="G52" t="n">
-        <v>2.09818451330239</v>
+        <v>2.03192119983401</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-1.05705438572106</v>
+        <v>-1.16268116079404</v>
       </c>
       <c r="B53" t="n">
-        <v>-1.0004039230423</v>
+        <v>-1.07507980926205</v>
       </c>
       <c r="C53" t="n">
-        <v>1.72979355331104</v>
+        <v>1.31343654422244</v>
       </c>
       <c r="D53" t="n">
-        <v>1.34877278913685</v>
+        <v>1.23554897916308</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.1336573791021</v>
+        <v>-0.828873770409173</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.53648627132077</v>
+        <v>-1.21333038947458</v>
       </c>
       <c r="G53" t="n">
-        <v>1.98543557086498</v>
+        <v>1.98855993476794</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-1.0292044213297</v>
+        <v>-1.32554363790865</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.97989313193546</v>
+        <v>-0.945090244828678</v>
       </c>
       <c r="C54" t="n">
-        <v>1.72529071375367</v>
+        <v>1.15328115462817</v>
       </c>
       <c r="D54" t="n">
-        <v>1.40064193507167</v>
+        <v>1.07650103808453</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.10594884789619</v>
+        <v>-0.41654527750341</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.26856850768837</v>
+        <v>-0.837160643941547</v>
       </c>
       <c r="G54" t="n">
-        <v>2.1249673261728</v>
+        <v>2.12241498164866</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-1.12629869409703</v>
+        <v>-0.560933939244957</v>
       </c>
       <c r="B55" t="n">
-        <v>-1.01421512959217</v>
+        <v>-0.890569830051674</v>
       </c>
       <c r="C55" t="n">
-        <v>1.50297881776788</v>
+        <v>0.903827564345075</v>
       </c>
       <c r="D55" t="n">
-        <v>1.6712605629086</v>
+        <v>0.0469620680829047</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.07039293143322</v>
+        <v>-1.26607796338292</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.11870246252148</v>
+        <v>-1.76549152479171</v>
       </c>
       <c r="G55" t="n">
-        <v>1.99238211403147</v>
+        <v>2.03404966106825</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-1.30333158707968</v>
+        <v>-0.831204908107467</v>
       </c>
       <c r="B56" t="n">
-        <v>-1.07670637084745</v>
+        <v>-1.1307209477557</v>
       </c>
       <c r="C56" t="n">
-        <v>1.55794854989029</v>
+        <v>1.23349841326728</v>
       </c>
       <c r="D56" t="n">
-        <v>1.65445034463568</v>
+        <v>0.871141339775438</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.599175689241086</v>
+        <v>-1.34237878559006</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.12009934085094</v>
+        <v>-1.8781598148852</v>
       </c>
       <c r="G56" t="n">
-        <v>1.87813419512887</v>
+        <v>2.02184393096599</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-1.14694809991514</v>
+        <v>-1.1611433837899</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.801797019217643</v>
+        <v>-1.23496206591772</v>
       </c>
       <c r="C57" t="n">
-        <v>1.17115497744941</v>
+        <v>1.51116332950694</v>
       </c>
       <c r="D57" t="n">
-        <v>1.59420662377863</v>
+        <v>1.02666510729082</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.951651559817215</v>
+        <v>-0.640666927404896</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.03935040165801</v>
+        <v>-1.1082023881458</v>
       </c>
       <c r="G57" t="n">
-        <v>2.12730702837416</v>
+        <v>2.02962284931026</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-1.00108521622008</v>
+        <v>-0.991636851333948</v>
       </c>
       <c r="B58" t="n">
-        <v>-1.27031495018487</v>
+        <v>-1.0130789735275</v>
       </c>
       <c r="C58" t="n">
-        <v>1.76254757854287</v>
+        <v>1.10772439305451</v>
       </c>
       <c r="D58" t="n">
-        <v>1.10256750834985</v>
+        <v>0.884923270023338</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.827749067414804</v>
+        <v>-1.04726946209446</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.47283825067807</v>
+        <v>-1.43382631547644</v>
       </c>
       <c r="G58" t="n">
-        <v>1.94031388089641</v>
+        <v>1.92345245238682</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-0.872675478741476</v>
+        <v>-1.34488444023348</v>
       </c>
       <c r="B59" t="n">
-        <v>-1.16784230452819</v>
+        <v>-1.04016015848001</v>
       </c>
       <c r="C59" t="n">
-        <v>1.82674647314459</v>
+        <v>1.08287892435908</v>
       </c>
       <c r="D59" t="n">
-        <v>0.86987855881452</v>
+        <v>1.50273300426184</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.02221617889158</v>
+        <v>-0.463184630293108</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.55556551784042</v>
+        <v>-1.03911205050476</v>
       </c>
       <c r="G59" t="n">
-        <v>2.07637691788919</v>
+        <v>2.02490054903106</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-0.890805445188083</v>
+        <v>-1.11288919146801</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.958605982088499</v>
+        <v>-1.14080066589143</v>
       </c>
       <c r="C60" t="n">
-        <v>1.364138051238</v>
+        <v>1.28268955641831</v>
       </c>
       <c r="D60" t="n">
-        <v>0.907751097558073</v>
+        <v>0.845227912180354</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.06006006095639</v>
+        <v>-0.922300174119304</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.68422717981203</v>
+        <v>-1.85596011847035</v>
       </c>
       <c r="G60" t="n">
-        <v>1.98576531297529</v>
+        <v>2.00693051844606</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-1.27661538988437</v>
+        <v>-1.19760335952842</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.11389878041896</v>
+        <v>-0.792177538284439</v>
       </c>
       <c r="C61" t="n">
-        <v>1.53157829533406</v>
+        <v>0.969830595441293</v>
       </c>
       <c r="D61" t="n">
-        <v>1.73655462821265</v>
+        <v>1.41155139817141</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.768642071412696</v>
+        <v>-0.520481901330542</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.19825231723309</v>
+        <v>-1.13839030770755</v>
       </c>
       <c r="G61" t="n">
-        <v>1.95179537646793</v>
+        <v>2.12312139405735</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-1.45599823097832</v>
+        <v>-1.19151353461971</v>
       </c>
       <c r="B62" t="n">
-        <v>-1.14476326696001</v>
+        <v>-1.04656322466211</v>
       </c>
       <c r="C62" t="n">
-        <v>1.79793596602453</v>
+        <v>1.19364490816937</v>
       </c>
       <c r="D62" t="n">
-        <v>1.87820329767163</v>
+        <v>1.31410371415119</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.741367507861648</v>
+        <v>-0.708301594213876</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.77816530244858</v>
+        <v>-1.27162325303268</v>
       </c>
       <c r="G62" t="n">
-        <v>2.06295643762023</v>
+        <v>2.03605106749916</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-1.1274335034793</v>
+        <v>-0.878681439394008</v>
       </c>
       <c r="B63" t="n">
-        <v>-1.08633607609706</v>
+        <v>-1.0953106774245</v>
       </c>
       <c r="C63" t="n">
-        <v>1.56183307066522</v>
+        <v>1.26265510279685</v>
       </c>
       <c r="D63" t="n">
-        <v>1.45877603101864</v>
+        <v>0.569315817121266</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.745501206640728</v>
+        <v>-1.19128693988546</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.34493117815934</v>
+        <v>-2.43159671156702</v>
       </c>
       <c r="G63" t="n">
-        <v>2.06910430821237</v>
+        <v>1.97000541073399</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-0.930205035084205</v>
+        <v>-1.17201521847909</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.930333725204255</v>
+        <v>-1.08079021423168</v>
       </c>
       <c r="C64" t="n">
-        <v>1.41108494943512</v>
+        <v>1.17193371283439</v>
       </c>
       <c r="D64" t="n">
-        <v>1.33955731594561</v>
+        <v>1.40391157694641</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.48557930594594</v>
+        <v>-0.800018751762877</v>
       </c>
       <c r="F64" t="n">
-        <v>-2.73369628803778</v>
+        <v>-1.37755034792658</v>
       </c>
       <c r="G64" t="n">
-        <v>1.84652918314644</v>
+        <v>1.96696490168582</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-0.952499760395403</v>
+        <v>-1.15756725573246</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.816490628801611</v>
+        <v>-0.762948988199171</v>
       </c>
       <c r="C65" t="n">
-        <v>1.38696283892298</v>
+        <v>0.695182509802999</v>
       </c>
       <c r="D65" t="n">
-        <v>1.0380994296293</v>
+        <v>1.45632374636958</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.894289814129152</v>
+        <v>-1.05936076521106</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.61967293866333</v>
+        <v>-1.36716291186687</v>
       </c>
       <c r="G65" t="n">
-        <v>2.10910556286986</v>
+        <v>2.00452261950219</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-0.965225494021211</v>
+        <v>-1.07480343881791</v>
       </c>
       <c r="B66" t="n">
-        <v>-1.06579607491538</v>
+        <v>-0.878300913836612</v>
       </c>
       <c r="C66" t="n">
-        <v>1.63600218858921</v>
+        <v>0.987022787973625</v>
       </c>
       <c r="D66" t="n">
-        <v>0.890532083638065</v>
+        <v>1.35380664749266</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.818086196997407</v>
+        <v>-1.13615453633913</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.34643046756581</v>
+        <v>-1.49308355573714</v>
       </c>
       <c r="G66" t="n">
-        <v>2.0717770630413</v>
+        <v>2.0079511834969</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-0.810392159897162</v>
+        <v>-1.07394661280134</v>
       </c>
       <c r="B67" t="n">
-        <v>-1.33033968248022</v>
+        <v>-0.811168251018829</v>
       </c>
       <c r="C67" t="n">
-        <v>1.92710859919447</v>
+        <v>0.936891728738816</v>
       </c>
       <c r="D67" t="n">
-        <v>0.673021829602106</v>
+        <v>1.37512589808413</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.07524656211238</v>
+        <v>-0.974363600810908</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.71443589282891</v>
+        <v>-1.45006872480069</v>
       </c>
       <c r="G67" t="n">
-        <v>1.87632883756708</v>
+        <v>2.10648778992993</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-0.992466227594106</v>
+        <v>-1.06253843668365</v>
       </c>
       <c r="B68" t="n">
-        <v>-1.11699062782717</v>
+        <v>-0.76178773761694</v>
       </c>
       <c r="C68" t="n">
-        <v>1.99206416320345</v>
+        <v>0.778205839700017</v>
       </c>
       <c r="D68" t="n">
-        <v>0.804102753885418</v>
+        <v>1.18722994676915</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.980302764714693</v>
+        <v>-1.22511063232012</v>
       </c>
       <c r="F68" t="n">
-        <v>-2.06272880058061</v>
+        <v>-1.49302194007751</v>
       </c>
       <c r="G68" t="n">
-        <v>2.03728483313028</v>
+        <v>1.94197039173594</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-1.21788544046589</v>
+        <v>-0.777350463947264</v>
       </c>
       <c r="B69" t="n">
-        <v>-1.13543556163784</v>
+        <v>-1.05363843477204</v>
       </c>
       <c r="C69" t="n">
-        <v>1.74688252591654</v>
+        <v>1.06286418288164</v>
       </c>
       <c r="D69" t="n">
-        <v>1.41930689497831</v>
+        <v>0.328783198480306</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.361934546699522</v>
+        <v>-1.55157979227204</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.03939717317869</v>
+        <v>-1.71140206889732</v>
       </c>
       <c r="G69" t="n">
-        <v>2.09225276890614</v>
+        <v>1.63685901958765</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-1.06567687141023</v>
+        <v>-1.09039906641316</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.821418827755283</v>
+        <v>-1.14945390026475</v>
       </c>
       <c r="C70" t="n">
-        <v>1.37262541130506</v>
+        <v>1.38181942354178</v>
       </c>
       <c r="D70" t="n">
-        <v>1.28104043125954</v>
+        <v>1.06711160406827</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.976072688946621</v>
+        <v>-0.786834737981444</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.44498815921785</v>
+        <v>-1.26783361415069</v>
       </c>
       <c r="G70" t="n">
-        <v>1.90259623926925</v>
+        <v>2.03232042643049</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-1.11031047128336</v>
+        <v>-1.07527753608422</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.850778996782684</v>
+        <v>-1.10880247031944</v>
       </c>
       <c r="C71" t="n">
-        <v>1.33186235781573</v>
+        <v>1.09581299196979</v>
       </c>
       <c r="D71" t="n">
-        <v>1.40825255628355</v>
+        <v>1.1782659823606</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.834860032914283</v>
+        <v>-1.25829536595239</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.4621315213431</v>
+        <v>-1.5149767536589</v>
       </c>
       <c r="G71" t="n">
-        <v>1.96989257320769</v>
+        <v>1.96110484743694</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-0.912037376512143</v>
+        <v>-0.924833155240653</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.788266055147149</v>
+        <v>-0.885730893566207</v>
       </c>
       <c r="C72" t="n">
-        <v>1.3673378139025</v>
+        <v>0.861514340807454</v>
       </c>
       <c r="D72" t="n">
-        <v>0.912417060050328</v>
+        <v>0.630123727519298</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.721265049756022</v>
+        <v>-0.874550829831827</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.57029937169515</v>
+        <v>-1.41416213085131</v>
       </c>
       <c r="G72" t="n">
-        <v>2.07756627227928</v>
+        <v>1.98729533519732</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-1.28670760876017</v>
+        <v>-1.28060123350005</v>
       </c>
       <c r="B73" t="n">
-        <v>-1.07514419079129</v>
+        <v>-0.820419930375405</v>
       </c>
       <c r="C73" t="n">
-        <v>1.67559826161873</v>
+        <v>0.941472429986346</v>
       </c>
       <c r="D73" t="n">
-        <v>1.21008208509178</v>
+        <v>1.36443741460201</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.737059333485313</v>
+        <v>-0.249224639747762</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.51028970820955</v>
+        <v>-1.06178007788594</v>
       </c>
       <c r="G73" t="n">
-        <v>2.08513934188628</v>
+        <v>2.05840756391556</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-1.09892774442586</v>
+        <v>-0.822133065427827</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.766080451854663</v>
+        <v>-0.818503387959051</v>
       </c>
       <c r="C74" t="n">
-        <v>1.28104955576097</v>
+        <v>0.707794451724005</v>
       </c>
       <c r="D74" t="n">
-        <v>1.15513351251896</v>
+        <v>0.660236369170231</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.767514422671115</v>
+        <v>-1.20951316180911</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.23695803150181</v>
+        <v>-1.55039987803116</v>
       </c>
       <c r="G74" t="n">
-        <v>1.86657932261641</v>
+        <v>2.09366452761334</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-0.872862650509298</v>
+        <v>-0.930917420106594</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.914561691818927</v>
+        <v>-0.9733202928574</v>
       </c>
       <c r="C75" t="n">
-        <v>1.54550322089831</v>
+        <v>1.01661116612149</v>
       </c>
       <c r="D75" t="n">
-        <v>1.08234648820577</v>
+        <v>0.787160209008848</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.785655288716568</v>
+        <v>-0.737832170841048</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.5928177814978</v>
+        <v>-1.47484682306702</v>
       </c>
       <c r="G75" t="n">
-        <v>2.08165363115825</v>
+        <v>2.05741175514283</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-1.21776728783758</v>
+        <v>-1.02663856609041</v>
       </c>
       <c r="B76" t="n">
-        <v>-1.263018704888</v>
+        <v>-1.08725815472789</v>
       </c>
       <c r="C76" t="n">
-        <v>1.70637381395748</v>
+        <v>1.11877409783493</v>
       </c>
       <c r="D76" t="n">
-        <v>1.68740211622337</v>
+        <v>1.0504627780123</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.862564478569189</v>
+        <v>-0.890796124542633</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.36258949314141</v>
+        <v>-1.46641652230213</v>
       </c>
       <c r="G76" t="n">
-        <v>1.96345120972484</v>
+        <v>1.99354966097543</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-1.55410315476831</v>
+        <v>-1.00268796060863</v>
       </c>
       <c r="B77" t="n">
-        <v>-0.981110917682651</v>
+        <v>-0.838707053135389</v>
       </c>
       <c r="C77" t="n">
-        <v>1.47580015286208</v>
+        <v>0.794163556524087</v>
       </c>
       <c r="D77" t="n">
-        <v>1.97126068269721</v>
+        <v>0.923438416770121</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.279918869373196</v>
+        <v>-1.15124945289409</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.746341556946165</v>
+        <v>-1.43337150521742</v>
       </c>
       <c r="G77" t="n">
-        <v>1.90497851810445</v>
+        <v>2.03111434872405</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-1.09052002504909</v>
+        <v>-1.2918643018415</v>
       </c>
       <c r="B78" t="n">
-        <v>-1.00075384484549</v>
+        <v>-1.19726670720641</v>
       </c>
       <c r="C78" t="n">
-        <v>1.63125795830632</v>
+        <v>1.13945428540445</v>
       </c>
       <c r="D78" t="n">
-        <v>1.37169295315432</v>
+        <v>1.03580873062994</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.593079384463097</v>
+        <v>-0.517218297863703</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.35749001297186</v>
+        <v>-1.47963450502016</v>
       </c>
       <c r="G78" t="n">
-        <v>2.13189639998532</v>
+        <v>1.95721424016383</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-1.00016454526628</v>
+        <v>-1.01446824282218</v>
       </c>
       <c r="B79" t="n">
-        <v>-0.988029470883915</v>
+        <v>-1.03930277991506</v>
       </c>
       <c r="C79" t="n">
-        <v>1.55857608969054</v>
+        <v>1.14123552338299</v>
       </c>
       <c r="D79" t="n">
-        <v>1.43965336158492</v>
+        <v>0.958851999275075</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.1055704385926</v>
+        <v>-0.55060888775684</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.64050285753356</v>
+        <v>-1.30613268038661</v>
       </c>
       <c r="G79" t="n">
-        <v>2.04408507909673</v>
+        <v>2.07647455448696</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-0.912174612635741</v>
+        <v>-1.07544305935022</v>
       </c>
       <c r="B80" t="n">
-        <v>-1.05075482245107</v>
+        <v>-0.976145153822457</v>
       </c>
       <c r="C80" t="n">
-        <v>1.60376014281892</v>
+        <v>1.1013079784673</v>
       </c>
       <c r="D80" t="n">
-        <v>0.842339919981667</v>
+        <v>1.11345829283481</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.24806079922654</v>
+        <v>-0.594166566835049</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.07866457921331</v>
+        <v>-1.32367539057578</v>
       </c>
       <c r="G80" t="n">
-        <v>2.03562333043407</v>
+        <v>2.08881402072612</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-1.04136299533906</v>
+        <v>-1.16188380302492</v>
       </c>
       <c r="B81" t="n">
-        <v>-1.08180630402559</v>
+        <v>-1.13336251998427</v>
       </c>
       <c r="C81" t="n">
-        <v>1.80490697987203</v>
+        <v>1.31931445144271</v>
       </c>
       <c r="D81" t="n">
-        <v>0.974903244662176</v>
+        <v>1.133369301151</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.962889266179976</v>
+        <v>-0.76289421692967</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.88103249278367</v>
+        <v>-1.27658855971124</v>
       </c>
       <c r="G81" t="n">
-        <v>1.99410621569309</v>
+        <v>2.04484909303713</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-1.11682364711975</v>
+        <v>-0.711654276816916</v>
       </c>
       <c r="B82" t="n">
-        <v>-1.03725167966935</v>
+        <v>-0.965847463179043</v>
       </c>
       <c r="C82" t="n">
-        <v>1.69267323527365</v>
+        <v>1.23586869427094</v>
       </c>
       <c r="D82" t="n">
-        <v>1.6098521981008</v>
+        <v>0.460781110771138</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.05388177103525</v>
+        <v>-1.21902520031459</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.58667462016972</v>
+        <v>-1.75984355217577</v>
       </c>
       <c r="G82" t="n">
-        <v>1.93445127162062</v>
+        <v>2.15474367487471</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-1.21982274821187</v>
+        <v>-1.0771281140749</v>
       </c>
       <c r="B83" t="n">
-        <v>-0.77376724445409</v>
+        <v>-0.954961296876549</v>
       </c>
       <c r="C83" t="n">
-        <v>1.2590157263935</v>
+        <v>0.966011095956581</v>
       </c>
       <c r="D83" t="n">
-        <v>1.71650544511518</v>
+        <v>1.35497960582724</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.892314513565034</v>
+        <v>-0.818740775767265</v>
       </c>
       <c r="F83" t="n">
-        <v>-1.29880934517889</v>
+        <v>-1.48071402895717</v>
       </c>
       <c r="G83" t="n">
-        <v>1.99380364192488</v>
+        <v>2.03983855683445</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-1.05060997834745</v>
+        <v>-1.34303784568744</v>
       </c>
       <c r="B84" t="n">
-        <v>-0.972595497004276</v>
+        <v>-1.01699963257018</v>
       </c>
       <c r="C84" t="n">
-        <v>1.56539174457632</v>
+        <v>0.88454258795629</v>
       </c>
       <c r="D84" t="n">
-        <v>1.14623460967194</v>
+        <v>1.80648930035161</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.699345815833016</v>
+        <v>-0.953630459320952</v>
       </c>
       <c r="F84" t="n">
-        <v>-1.367560844213</v>
+        <v>-1.93374289051299</v>
       </c>
       <c r="G84" t="n">
-        <v>2.03610746281111</v>
+        <v>1.97923916635244</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-1.1878068019456</v>
+        <v>-1.30983619872891</v>
       </c>
       <c r="B85" t="n">
-        <v>-1.05330422019915</v>
+        <v>-1.11678164155469</v>
       </c>
       <c r="C85" t="n">
-        <v>1.58405488293012</v>
+        <v>1.11919475993956</v>
       </c>
       <c r="D85" t="n">
-        <v>1.35672081852797</v>
+        <v>1.24169366702574</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.70605959891676</v>
+        <v>-0.476622220194407</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.18396704413755</v>
+        <v>-0.915315743317371</v>
       </c>
       <c r="G85" t="n">
-        <v>1.99138209909954</v>
+        <v>1.95686769790795</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-0.797661693417896</v>
+        <v>-1.11734734194749</v>
       </c>
       <c r="B86" t="n">
-        <v>-1.12011213157232</v>
+        <v>-0.992693695192422</v>
       </c>
       <c r="C86" t="n">
-        <v>1.50643519564295</v>
+        <v>1.12399794431655</v>
       </c>
       <c r="D86" t="n">
-        <v>0.825185428224163</v>
+        <v>0.990395904169509</v>
       </c>
       <c r="E86" t="n">
-        <v>-1.2316802664818</v>
+        <v>-0.954108650980576</v>
       </c>
       <c r="F86" t="n">
-        <v>-1.78853732539279</v>
+        <v>-1.74935799885451</v>
       </c>
       <c r="G86" t="n">
-        <v>2.08603061318824</v>
+        <v>2.01767844564462</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-0.948476113825492</v>
+        <v>-1.22018442841734</v>
       </c>
       <c r="B87" t="n">
-        <v>-1.29528111675345</v>
+        <v>-0.908702375298468</v>
       </c>
       <c r="C87" t="n">
-        <v>1.63931325398732</v>
+        <v>0.964822962064191</v>
       </c>
       <c r="D87" t="n">
-        <v>0.845692023531284</v>
+        <v>1.41617069129275</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.891855807193554</v>
+        <v>-0.931254728698521</v>
       </c>
       <c r="F87" t="n">
-        <v>-1.36016062466377</v>
+        <v>-1.35599907754864</v>
       </c>
       <c r="G87" t="n">
-        <v>1.97636390076342</v>
+        <v>1.9174738981803</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-1.24065207612264</v>
+        <v>-1.05063652605816</v>
       </c>
       <c r="B88" t="n">
-        <v>-1.03585701709396</v>
+        <v>-0.720869690888919</v>
       </c>
       <c r="C88" t="n">
-        <v>1.4517319389003</v>
+        <v>0.777385553724974</v>
       </c>
       <c r="D88" t="n">
-        <v>1.83129876667478</v>
+        <v>1.28244989552265</v>
       </c>
       <c r="E88" t="n">
-        <v>-1.15735957646785</v>
+        <v>-1.02783758771454</v>
       </c>
       <c r="F88" t="n">
-        <v>-2.42484767145559</v>
+        <v>-1.63699202413513</v>
       </c>
       <c r="G88" t="n">
-        <v>2.01447673750556</v>
+        <v>1.99694496976457</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-1.24527890531026</v>
+        <v>-1.13452663846284</v>
       </c>
       <c r="B89" t="n">
-        <v>-1.1509144079688</v>
+        <v>-0.982147713839902</v>
       </c>
       <c r="C89" t="n">
-        <v>1.77087563321016</v>
+        <v>1.07125387147865</v>
       </c>
       <c r="D89" t="n">
-        <v>1.63172014077584</v>
+        <v>1.39597896970192</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.469272491065182</v>
+        <v>-0.75099678789644</v>
       </c>
       <c r="F89" t="n">
-        <v>-1.22850733541463</v>
+        <v>-1.32776256956907</v>
       </c>
       <c r="G89" t="n">
-        <v>1.96255031266412</v>
+        <v>2.08823262994302</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-1.01776845574217</v>
+        <v>-0.9127997012959</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.991403775392121</v>
+        <v>-1.14130417430136</v>
       </c>
       <c r="C90" t="n">
-        <v>1.52236244887387</v>
+        <v>1.22139007071228</v>
       </c>
       <c r="D90" t="n">
-        <v>1.22431038981941</v>
+        <v>0.811694559264654</v>
       </c>
       <c r="E90" t="n">
-        <v>-1.30748236924735</v>
+        <v>-1.25178769110734</v>
       </c>
       <c r="F90" t="n">
-        <v>-1.59350143910786</v>
+        <v>-2.36781953959025</v>
       </c>
       <c r="G90" t="n">
-        <v>2.02812621364897</v>
+        <v>2.00657170854066</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-0.978092280064292</v>
+        <v>-1.29039408462281</v>
       </c>
       <c r="B91" t="n">
-        <v>-0.87165934226627</v>
+        <v>-0.936229891545281</v>
       </c>
       <c r="C91" t="n">
-        <v>1.42474277541532</v>
+        <v>1.04650788978611</v>
       </c>
       <c r="D91" t="n">
-        <v>1.37219212561472</v>
+        <v>1.36200194836684</v>
       </c>
       <c r="E91" t="n">
-        <v>-1.24100212923094</v>
+        <v>-0.399256708750674</v>
       </c>
       <c r="F91" t="n">
-        <v>-1.64119852767748</v>
+        <v>-0.921732392876633</v>
       </c>
       <c r="G91" t="n">
-        <v>2.14676630199379</v>
+        <v>1.96831587785865</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-1.11062268648115</v>
+        <v>-1.02815630339227</v>
       </c>
       <c r="B92" t="n">
-        <v>-0.895875210848972</v>
+        <v>-0.986142367473882</v>
       </c>
       <c r="C92" t="n">
-        <v>1.43789280704971</v>
+        <v>1.05810870779064</v>
       </c>
       <c r="D92" t="n">
-        <v>1.58765287088428</v>
+        <v>0.91398650049663</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.863960714093492</v>
+        <v>-1.06527608692288</v>
       </c>
       <c r="F92" t="n">
-        <v>-1.37961640128954</v>
+        <v>-2.05466782591847</v>
       </c>
       <c r="G92" t="n">
-        <v>1.99918343853709</v>
+        <v>2.07300990122033</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-1.16652266706751</v>
+        <v>-0.710849138439776</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.80772857548475</v>
+        <v>-0.95559001931884</v>
       </c>
       <c r="C93" t="n">
-        <v>1.37359859028914</v>
+        <v>0.968558797819435</v>
       </c>
       <c r="D93" t="n">
-        <v>1.71188237254039</v>
+        <v>0.60746151173935</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.684149278287938</v>
+        <v>-1.50632560203513</v>
       </c>
       <c r="F93" t="n">
-        <v>-1.46694286245373</v>
+        <v>-1.88896256707549</v>
       </c>
       <c r="G93" t="n">
-        <v>2.0306237538186</v>
+        <v>1.85826156337069</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-1.06022918226136</v>
+        <v>-1.27835274553609</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.971892263643122</v>
+        <v>-1.30183626961579</v>
       </c>
       <c r="C94" t="n">
-        <v>1.56923055333066</v>
+        <v>1.31846730469359</v>
       </c>
       <c r="D94" t="n">
-        <v>1.35679930814756</v>
+        <v>1.33671458505574</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.03222597577499</v>
+        <v>-0.391965087297585</v>
       </c>
       <c r="F94" t="n">
-        <v>-1.43308713755457</v>
+        <v>-1.00921126235356</v>
       </c>
       <c r="G94" t="n">
-        <v>2.10107853499467</v>
+        <v>1.97976760732813</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-1.2215499809739</v>
+        <v>-1.20277566789406</v>
       </c>
       <c r="B95" t="n">
-        <v>-1.05241929339347</v>
+        <v>-0.900054035697595</v>
       </c>
       <c r="C95" t="n">
-        <v>1.59802757419062</v>
+        <v>1.04049209527321</v>
       </c>
       <c r="D95" t="n">
-        <v>1.40375245543471</v>
+        <v>1.30361447276514</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.929781210008048</v>
+        <v>-0.817879311240297</v>
       </c>
       <c r="F95" t="n">
-        <v>-1.87394344038333</v>
+        <v>-1.15060716786991</v>
       </c>
       <c r="G95" t="n">
-        <v>2.04192549689571</v>
+        <v>2.08638893349104</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-1.02426226485613</v>
+        <v>-1.03294905101204</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.943588138966861</v>
+        <v>-1.0497753550698</v>
       </c>
       <c r="C96" t="n">
-        <v>1.64302409953448</v>
+        <v>1.17242757162453</v>
       </c>
       <c r="D96" t="n">
-        <v>1.28663085038982</v>
+        <v>0.957249656155771</v>
       </c>
       <c r="E96" t="n">
-        <v>-1.1652123457817</v>
+        <v>-1.10235857306857</v>
       </c>
       <c r="F96" t="n">
-        <v>-2.17257753682065</v>
+        <v>-2.27648312879907</v>
       </c>
       <c r="G96" t="n">
-        <v>2.03569553846758</v>
+        <v>2.01599437627982</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-1.11371053012101</v>
+        <v>-1.2708673486257</v>
       </c>
       <c r="B97" t="n">
-        <v>-1.09751496497742</v>
+        <v>-1.10369532645866</v>
       </c>
       <c r="C97" t="n">
-        <v>1.62423133283669</v>
+        <v>1.19822850035701</v>
       </c>
       <c r="D97" t="n">
-        <v>1.27057024506509</v>
+        <v>1.19199766940605</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.974013963736758</v>
+        <v>-0.928652942859236</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.33346160728958</v>
+        <v>-1.68914686034849</v>
       </c>
       <c r="G97" t="n">
-        <v>1.95257101465684</v>
+        <v>1.98329014076625</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-1.1651510580332</v>
+        <v>-0.974862939937342</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.98005216006875</v>
+        <v>-1.07201808441413</v>
       </c>
       <c r="C98" t="n">
-        <v>1.53444789554839</v>
+        <v>1.22387562127621</v>
       </c>
       <c r="D98" t="n">
-        <v>1.77190406744898</v>
+        <v>0.755594170164193</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.708519993126834</v>
+        <v>-0.908487095009134</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.27853897988535</v>
+        <v>-1.37046974805516</v>
       </c>
       <c r="G98" t="n">
-        <v>2.01285436565673</v>
+        <v>1.99997636551038</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-0.734139308413651</v>
+        <v>-0.70406588772135</v>
       </c>
       <c r="B99" t="n">
-        <v>-1.16461608972725</v>
+        <v>-0.851799827731034</v>
       </c>
       <c r="C99" t="n">
-        <v>1.62267485037225</v>
+        <v>0.727547219187572</v>
       </c>
       <c r="D99" t="n">
-        <v>0.484566049109348</v>
+        <v>0.619269335504289</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.35523452777453</v>
+        <v>-1.3034445198171</v>
       </c>
       <c r="F99" t="n">
-        <v>-2.65124099864557</v>
+        <v>-1.87276721091199</v>
       </c>
       <c r="G99" t="n">
-        <v>1.98178133393916</v>
+        <v>1.99905418509434</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-1.18929757560552</v>
+        <v>-1.18991446719954</v>
       </c>
       <c r="B100" t="n">
-        <v>-0.928429770537388</v>
+        <v>-0.900109092253158</v>
       </c>
       <c r="C100" t="n">
-        <v>1.45201010873174</v>
+        <v>1.08876314972408</v>
       </c>
       <c r="D100" t="n">
-        <v>1.751708189861</v>
+        <v>1.11589644621972</v>
       </c>
       <c r="E100" t="n">
-        <v>-1.06373665187039</v>
+        <v>-0.699710879902149</v>
       </c>
       <c r="F100" t="n">
-        <v>-2.18714735323121</v>
+        <v>-1.21004699075989</v>
       </c>
       <c r="G100" t="n">
-        <v>1.98837138854506</v>
+        <v>1.99932570689287</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-1.164297855703</v>
+        <v>-1.3965969765687</v>
       </c>
       <c r="B101" t="n">
-        <v>-1.10750055017331</v>
+        <v>-0.837125869901079</v>
       </c>
       <c r="C101" t="n">
-        <v>1.68306671947727</v>
+        <v>0.854909579607373</v>
       </c>
       <c r="D101" t="n">
-        <v>1.40549612355935</v>
+        <v>1.6617344717685</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.898544475224145</v>
+        <v>-0.305185134304576</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.33348454104605</v>
+        <v>-0.883185647002824</v>
       </c>
       <c r="G101" t="n">
-        <v>1.94138515030529</v>
+        <v>2.14119928997168</v>
       </c>
     </row>
   </sheetData>
@@ -3149,826 +3152,826 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.16625134479912</v>
+        <v>3.37745487565417</v>
       </c>
       <c r="B2" t="n">
-        <v>0.196854713453101</v>
+        <v>0.372151635847571</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.117300296237203</v>
+        <v>9.14842717176527</v>
       </c>
       <c r="B3" t="n">
-        <v>0.049871528118213</v>
+        <v>0.350619962625347</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.152831795422507</v>
+        <v>0.19506031527317</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0910179591654642</v>
+        <v>0.111491042602577</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.54659984924928</v>
+        <v>6.01129141108662</v>
       </c>
       <c r="B5" t="n">
-        <v>0.237464747101746</v>
+        <v>0.369015970167207</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.175735555284994</v>
+        <v>0.233290446908108</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0783432128633139</v>
+        <v>0.104241313037391</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.062246105096921</v>
+        <v>0.136559451728434</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0550543668432537</v>
+        <v>0.296231119922069</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0678892395335097</v>
+        <v>29.224385290235</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0546313179431704</v>
+        <v>0.548695594150694</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.43398020468621</v>
+        <v>1.00074481292174</v>
       </c>
       <c r="B9" t="n">
-        <v>0.259884720556976</v>
+        <v>0.212110374061201</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6.16466309706108</v>
+        <v>0.177129540246572</v>
       </c>
       <c r="B10" t="n">
-        <v>0.349884758860933</v>
+        <v>0.249259195004964</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>24.5951386672241</v>
+        <v>3.39150059227398</v>
       </c>
       <c r="B11" t="n">
-        <v>0.375106276135516</v>
+        <v>0.266448720404201</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.297749326707056</v>
+        <v>17.8525713837273</v>
       </c>
       <c r="B12" t="n">
-        <v>0.290868590531486</v>
+        <v>0.372153982337205</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0840534018152091</v>
+        <v>18.382188825032</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0876504442930179</v>
+        <v>0.395949954886598</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9.19239710669964</v>
+        <v>3.92038439572308</v>
       </c>
       <c r="B14" t="n">
-        <v>0.366193335981838</v>
+        <v>0.311672848718372</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6.84809911257401</v>
+        <v>0.251370924084686</v>
       </c>
       <c r="B15" t="n">
-        <v>0.33504725568331</v>
+        <v>0.197192815605726</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1.59023507800744</v>
+        <v>0.307235009157255</v>
       </c>
       <c r="B16" t="n">
-        <v>0.242747338307411</v>
+        <v>0.246753473696988</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.46326039842758</v>
+        <v>0.148126746808437</v>
       </c>
       <c r="B17" t="n">
-        <v>0.185638598788055</v>
+        <v>0.617054220638134</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.707889558268706</v>
+        <v>0.209171718008068</v>
       </c>
       <c r="B18" t="n">
-        <v>0.319138170319183</v>
+        <v>0.0906408589962413</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.158191714776837</v>
+        <v>3.66541717002848</v>
       </c>
       <c r="B19" t="n">
-        <v>0.195839518131139</v>
+        <v>0.281700349768304</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.209560733266552</v>
+        <v>2.27805542611535</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0946155324295577</v>
+        <v>0.238562061685977</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.0306419993746116</v>
+        <v>0.191192548914166</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0468243295114224</v>
+        <v>0.200779291439007</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.183978972323534</v>
+        <v>0.411574176879586</v>
       </c>
       <c r="B22" t="n">
-        <v>0.28583631544443</v>
+        <v>0.35971716538609</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>12.7682240409493</v>
+        <v>0.107837563844612</v>
       </c>
       <c r="B23" t="n">
-        <v>0.38762950356701</v>
+        <v>0.0443904581535451</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2.0697789445344</v>
+        <v>0.118767789254044</v>
       </c>
       <c r="B24" t="n">
-        <v>0.195474237068521</v>
+        <v>0.275888205287769</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.480162952179193</v>
+        <v>98.5316807647244</v>
       </c>
       <c r="B25" t="n">
-        <v>0.29708704847992</v>
+        <v>0.536307599453274</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.121644852750376</v>
+        <v>0.197519083661895</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0713558588847034</v>
+        <v>0.138175787442869</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.751582940476492</v>
+        <v>0.68399591180029</v>
       </c>
       <c r="B27" t="n">
-        <v>0.275900503483725</v>
+        <v>0.360391214494095</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.181554954233406</v>
+        <v>0.169402531276381</v>
       </c>
       <c r="B28" t="n">
-        <v>0.092328406724869</v>
+        <v>0.183514836825555</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>13.2039648287568</v>
+        <v>0.161867596504542</v>
       </c>
       <c r="B29" t="n">
-        <v>0.329726613287648</v>
+        <v>0.0993954098929531</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.200560791483983</v>
+        <v>0.215016295616891</v>
       </c>
       <c r="B30" t="n">
-        <v>0.110931044407522</v>
+        <v>0.249752312314528</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.257135975451713</v>
+        <v>3.62980502357738</v>
       </c>
       <c r="B31" t="n">
-        <v>0.273192489645079</v>
+        <v>0.298661326468408</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.134127360685581</v>
+        <v>0.359615546422906</v>
       </c>
       <c r="B32" t="n">
-        <v>0.100568530877621</v>
+        <v>0.261732937011981</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.185843585331349</v>
+        <v>0.217988982990726</v>
       </c>
       <c r="B33" t="n">
-        <v>0.250371613314732</v>
+        <v>0.123285694837287</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.15020621601595</v>
+        <v>1.30761082004578</v>
       </c>
       <c r="B34" t="n">
-        <v>0.133527302467811</v>
+        <v>0.223540620432393</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.204873387547401</v>
+        <v>0.73455323027229</v>
       </c>
       <c r="B35" t="n">
-        <v>0.319597641867714</v>
+        <v>0.163224852852292</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2.5252856947148</v>
+        <v>0.228385943507424</v>
       </c>
       <c r="B36" t="n">
-        <v>0.27960540366578</v>
+        <v>0.0901859840737726</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.140576459399456</v>
+        <v>0.0699841117729952</v>
       </c>
       <c r="B37" t="n">
-        <v>0.0666627934728713</v>
+        <v>0.057626811538518</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1.55671178665236</v>
+        <v>12.5345091297045</v>
       </c>
       <c r="B38" t="n">
-        <v>0.208502144351572</v>
+        <v>0.381802216089353</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1.43454580763643</v>
+        <v>1.34239624459469</v>
       </c>
       <c r="B39" t="n">
-        <v>0.246540098665894</v>
+        <v>0.232275897755235</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.16170111637509</v>
+        <v>7.33638043189855</v>
       </c>
       <c r="B40" t="n">
-        <v>0.246877354664327</v>
+        <v>0.313146109974929</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.727149307875522</v>
+        <v>0.144516993068156</v>
       </c>
       <c r="B41" t="n">
-        <v>0.181668855453205</v>
+        <v>0.177072250312787</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2.29746559732774</v>
+        <v>0.0682931954892323</v>
       </c>
       <c r="B42" t="n">
-        <v>0.2553768339579</v>
+        <v>0.061249667488803</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>8.36217955387026</v>
+        <v>0.535080904217633</v>
       </c>
       <c r="B43" t="n">
-        <v>0.306977435676978</v>
+        <v>0.160354097929298</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.103987098331037</v>
+        <v>2.58587372153931</v>
       </c>
       <c r="B44" t="n">
-        <v>0.321696302098285</v>
+        <v>0.226331281231112</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.0927100414424046</v>
+        <v>0.266435375109681</v>
       </c>
       <c r="B45" t="n">
-        <v>0.059858032552882</v>
+        <v>0.302751490985142</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.0687006191380266</v>
+        <v>0.0553769993406836</v>
       </c>
       <c r="B46" t="n">
-        <v>0.036452587058439</v>
+        <v>0.0562447967307409</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.218975092797938</v>
+        <v>6.39729637620049</v>
       </c>
       <c r="B47" t="n">
-        <v>0.143664059012414</v>
+        <v>0.331037111870575</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1.02222106646641</v>
+        <v>0.198130556431627</v>
       </c>
       <c r="B48" t="n">
-        <v>0.221044717571659</v>
+        <v>0.0889507027921004</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.272800736436703</v>
+        <v>0.226386345017877</v>
       </c>
       <c r="B49" t="n">
-        <v>0.208663550608866</v>
+        <v>0.128012146339541</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.23088871898583</v>
+        <v>12.4230071813609</v>
       </c>
       <c r="B50" t="n">
-        <v>0.198053179466226</v>
+        <v>0.345015599467828</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>12.8656455925085</v>
+        <v>0.164129164628209</v>
       </c>
       <c r="B51" t="n">
-        <v>0.366793607057539</v>
+        <v>0.193002046689465</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.539734144326879</v>
+        <v>2.1054932384662</v>
       </c>
       <c r="B52" t="n">
-        <v>0.243874563833865</v>
+        <v>0.246914523119541</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3.69494391359772</v>
+        <v>0.0742224061209181</v>
       </c>
       <c r="B53" t="n">
-        <v>0.260610235787077</v>
+        <v>0.0335707532311559</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.662388158617885</v>
+        <v>0.346428378512993</v>
       </c>
       <c r="B54" t="n">
-        <v>0.392995056819069</v>
+        <v>0.51841751354264</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.197755336197323</v>
+        <v>44.7100979547184</v>
       </c>
       <c r="B55" t="n">
-        <v>0.346181551145807</v>
+        <v>0.431227830403218</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.201925433641098</v>
+        <v>40.3684655875688</v>
       </c>
       <c r="B56" t="n">
-        <v>0.142551028444927</v>
+        <v>0.481904966235393</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.129060243213867</v>
+        <v>0.131033547616648</v>
       </c>
       <c r="B57" t="n">
-        <v>0.318586279123124</v>
+        <v>0.13753043223054</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2.09625470378179</v>
+        <v>1.45102857627857</v>
       </c>
       <c r="B58" t="n">
-        <v>0.215455024549144</v>
+        <v>0.185357734540038</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>3.98620749269429</v>
+        <v>0.158086465157248</v>
       </c>
       <c r="B59" t="n">
-        <v>0.27364557861418</v>
+        <v>0.221343601925318</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>9.23466898570796</v>
+        <v>0.159557430929395</v>
       </c>
       <c r="B60" t="n">
-        <v>0.363233956347549</v>
+        <v>0.22224163621393</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.145195737346445</v>
+        <v>0.129759332843419</v>
       </c>
       <c r="B61" t="n">
-        <v>0.0633799967189088</v>
+        <v>0.106249065636813</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.299135241371881</v>
+        <v>0.061893386183521</v>
       </c>
       <c r="B62" t="n">
-        <v>0.287982740249448</v>
+        <v>0.0596711528882996</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.259059738696212</v>
+        <v>0.911975807872954</v>
       </c>
       <c r="B63" t="n">
-        <v>0.119831747105838</v>
+        <v>0.320147163326426</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>59.6806484847675</v>
+        <v>0.292665144836167</v>
       </c>
       <c r="B64" t="n">
-        <v>0.538129292163346</v>
+        <v>0.147328388723978</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4.79504526509039</v>
+        <v>0.639292021019717</v>
       </c>
       <c r="B65" t="n">
-        <v>0.31009893947936</v>
+        <v>0.150852844932548</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.313379503903738</v>
+        <v>1.70733440554995</v>
       </c>
       <c r="B66" t="n">
-        <v>0.119586911605867</v>
+        <v>0.243364803330111</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>12.0862149735506</v>
+        <v>2.22967897096783</v>
       </c>
       <c r="B67" t="n">
-        <v>0.387946417358514</v>
+        <v>0.199680882345979</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.165890409353304</v>
+        <v>3.24325289405813</v>
       </c>
       <c r="B68" t="n">
-        <v>0.261161869222664</v>
+        <v>0.24436679421432</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.243866377156137</v>
+        <v>14.3971004305522</v>
       </c>
       <c r="B69" t="n">
-        <v>0.22885149570452</v>
+        <v>0.38971860682567</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.8644703657617</v>
+        <v>0.0876229036826246</v>
       </c>
       <c r="B70" t="n">
-        <v>0.196567691503354</v>
+        <v>0.0620530849272121</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1.39620038096149</v>
+        <v>2.48592253665418</v>
       </c>
       <c r="B71" t="n">
-        <v>0.200435132205395</v>
+        <v>0.251146724508457</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4.70606671486415</v>
+        <v>0.915485549721536</v>
       </c>
       <c r="B72" t="n">
-        <v>0.284043965568513</v>
+        <v>0.173609238327415</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.195972895005421</v>
+        <v>0.234794980591524</v>
       </c>
       <c r="B73" t="n">
-        <v>0.230593266330422</v>
+        <v>0.20733065134709</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.0525781759178905</v>
+        <v>5.34386667370433</v>
       </c>
       <c r="B74" t="n">
-        <v>0.0378922047403114</v>
+        <v>0.287785844048724</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>5.59951903100697</v>
+        <v>1.98417259507108</v>
       </c>
       <c r="B75" t="n">
-        <v>0.297239828831469</v>
+        <v>0.2065083708289</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.205298774614959</v>
+        <v>1.21029692915413</v>
       </c>
       <c r="B76" t="n">
-        <v>0.13423043532391</v>
+        <v>0.213826922158347</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.503791921290482</v>
+        <v>0.733364006429071</v>
       </c>
       <c r="B77" t="n">
-        <v>0.665721319997008</v>
+        <v>0.189217959547411</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.353782227540302</v>
+        <v>0.200740991751495</v>
       </c>
       <c r="B78" t="n">
-        <v>0.130606286675142</v>
+        <v>0.29436389150985</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>5.02589698904113</v>
+        <v>0.15383217580641</v>
       </c>
       <c r="B79" t="n">
-        <v>0.335812365798443</v>
+        <v>0.0823383630634557</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.33307341283771</v>
+        <v>0.162584635145589</v>
       </c>
       <c r="B80" t="n">
-        <v>0.279965214301733</v>
+        <v>0.105063751182463</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.184082432194364</v>
+        <v>0.057567987672515</v>
       </c>
       <c r="B81" t="n">
-        <v>0.21710873559093</v>
+        <v>0.0656668678399118</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4.29747281450102</v>
+        <v>16.5760431645493</v>
       </c>
       <c r="B82" t="n">
-        <v>0.292226306114942</v>
+        <v>0.41544266009428</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.20406604554589</v>
+        <v>1.20317568384673</v>
       </c>
       <c r="B83" t="n">
-        <v>0.0848627193652355</v>
+        <v>0.222130161835496</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.348699983165943</v>
+        <v>0.239464388939972</v>
       </c>
       <c r="B84" t="n">
-        <v>0.131660848189655</v>
+        <v>0.206074886692525</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.131333642299906</v>
+        <v>0.268213035069256</v>
       </c>
       <c r="B85" t="n">
-        <v>0.0702260758945721</v>
+        <v>0.390227916998876</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>15.1457544697016</v>
+        <v>0.213513807645313</v>
       </c>
       <c r="B86" t="n">
-        <v>0.429500864345888</v>
+        <v>0.189055833897755</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.377912486179293</v>
+        <v>0.158099019212879</v>
       </c>
       <c r="B87" t="n">
-        <v>0.126658011059692</v>
+        <v>0.130216948976396</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.47987076402404</v>
+        <v>5.20684002068321</v>
       </c>
       <c r="B88" t="n">
-        <v>0.252722479036978</v>
+        <v>0.3499906804239</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.0454696093272165</v>
+        <v>0.44749377060077</v>
       </c>
       <c r="B89" t="n">
-        <v>0.0296670059657348</v>
+        <v>0.110987920297375</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4.78273316185319</v>
+        <v>1.28139766003548</v>
       </c>
       <c r="B90" t="n">
-        <v>0.296516825774783</v>
+        <v>0.4122813652018</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>6.71588121149033</v>
+        <v>0.402382020640771</v>
       </c>
       <c r="B91" t="n">
-        <v>0.336084195714064</v>
+        <v>0.362581737689879</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.582530114801087</v>
+        <v>0.135360996130363</v>
       </c>
       <c r="B92" t="n">
-        <v>0.143073666385951</v>
+        <v>0.295985218647846</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1.79069603879271</v>
+        <v>42.5329531190471</v>
       </c>
       <c r="B93" t="n">
-        <v>0.204760296328908</v>
+        <v>0.485058541780176</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.826956885248001</v>
+        <v>0.382849490756879</v>
       </c>
       <c r="B94" t="n">
-        <v>0.187725002423009</v>
+        <v>0.2655661869689</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.105886402558176</v>
+        <v>0.156400469081833</v>
       </c>
       <c r="B95" t="n">
-        <v>0.280479272819431</v>
+        <v>0.0984511471578367</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.48110954609362</v>
+        <v>0.151532146522836</v>
       </c>
       <c r="B96" t="n">
-        <v>0.288948539408237</v>
+        <v>0.447150254511368</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.432760757004154</v>
+        <v>0.278389787309056</v>
       </c>
       <c r="B97" t="n">
-        <v>0.110555531258483</v>
+        <v>0.201110986290003</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.0977892596773367</v>
+        <v>0.725542169477884</v>
       </c>
       <c r="B98" t="n">
-        <v>0.0635913415971191</v>
+        <v>0.153402807022353</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>15.6935655695874</v>
+        <v>68.3422780351392</v>
       </c>
       <c r="B99" t="n">
-        <v>0.513987797818706</v>
+        <v>0.469252937348612</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.275737227061378</v>
+        <v>0.0632614838810419</v>
       </c>
       <c r="B100" t="n">
-        <v>0.217474337281396</v>
+        <v>0.0291211652654676</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.195990436550779</v>
+        <v>0.307611576941118</v>
       </c>
       <c r="B101" t="n">
-        <v>0.10539840612519</v>
+        <v>0.443297295571793</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2.90204222566705</v>
+        <v>5.17285395836594</v>
       </c>
       <c r="B104" t="n">
-        <v>0.224350794339221</v>
+        <v>0.244519484333458</v>
       </c>
     </row>
   </sheetData>
@@ -3984,18 +3987,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46016.7590286954</v>
+        <v>46026.05572942</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
